--- a/output/ATIQ GRUPO LOGISTICS.xlsx
+++ b/output/ATIQ GRUPO LOGISTICS.xlsx
@@ -1,125 +1,52 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maric\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D5344E1-86A8-4B80-B6DC-B1CE9449EB5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{6F36AFD9-B07A-4120-8C17-9B9B96AC2EF3}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="IMPO118" sheetId="1" r:id="rId1"/>
-    <sheet name="IMPO235" sheetId="2" r:id="rId2"/>
-    <sheet name="EXPO118" sheetId="3" r:id="rId3"/>
-    <sheet name="EXPO235" sheetId="4" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMPO118" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMPO235" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EXPO118" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EXPO235" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMPO118-Transmisiones" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="15">
-  <si>
-    <t>N°</t>
-  </si>
-  <si>
-    <t>MASTER</t>
-  </si>
-  <si>
-    <t>NUMERO DE PROCESO</t>
-  </si>
-  <si>
-    <t>NUMERO DE MANIFIESTO</t>
-  </si>
-  <si>
-    <t>CODIGO DE PUERTO</t>
-  </si>
-  <si>
-    <t>PUERTO</t>
-  </si>
-  <si>
-    <t>CNT</t>
-  </si>
-  <si>
-    <t>TIPO DE NUMERACION</t>
-  </si>
-  <si>
-    <t>FECHA Y HORA DE  NUMERACION INICIAL</t>
-  </si>
-  <si>
-    <t>FECHA Y HORA DE TRANSMISION DE LA LINEA</t>
-  </si>
-  <si>
-    <t>FECHA Y HORA DE INFORMACION COMPLEMENTARIA</t>
-  </si>
-  <si>
-    <t>FECHA Y HORA DE LLEGADA DE LA NAVE</t>
-  </si>
-  <si>
-    <t>ESTADO (MULTA)</t>
-  </si>
-  <si>
-    <t>FECHA Y HORA DE  TRANSMISION AGTE. DE CARGA</t>
-  </si>
-  <si>
-    <t>FECHA Y HORA DE TERMINO DE EMBARQUE</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="8"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="8"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -152,39 +79,98 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -504,49 +490,79 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05289A66-F660-4D3D-BBFC-B812FC1D9810}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
+    <row r="1" ht="43.2" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>N°</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>MASTER</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>NUMERO DE PROCESO</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>NUMERO DE MANIFIESTO</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>CODIGO DE PUERTO</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>PUERTO</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>CNT</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>TIPO DE NUMERACION</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>FECHA Y HORA DE  NUMERACION INICIAL</t>
+        </is>
+      </c>
+      <c r="J1" s="6" t="inlineStr">
+        <is>
+          <t>FECHA Y HORA DE TRANSMISION DE LA LINEA</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>FECHA Y HORA DE INFORMACION COMPLEMENTARIA</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>FECHA Y HORA DE LLEGADA DE LA NAVE</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ESTADO (MULTA)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -555,46 +571,74 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84F711BF-FB44-48D0-AC5C-C466CD98967A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>12</v>
+    <row r="1" ht="43.2" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>N°</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>MASTER</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>NUMERO DE PROCESO</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>NUMERO DE MANIFIESTO</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>CODIGO DE PUERTO</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>PUERTO</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>TIPO DE NUMERACION</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>FECHA Y HORA DE  NUMERACION INICIAL</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>FECHA Y HORA DE TRANSMISION DE LA LINEA</t>
+        </is>
+      </c>
+      <c r="J1" s="6" t="inlineStr">
+        <is>
+          <t>FECHA Y HORA DE INFORMACION COMPLEMENTARIA</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>FECHA Y HORA DE LLEGADA DE LA NAVE</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>ESTADO (MULTA)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -603,37 +647,59 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69585CB0-9F9B-40BB-BE0C-31222A672CCB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>12</v>
+    <row r="1" ht="32.4" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>N°</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>MASTER</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>NUMERO DE PROCESO</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>NUMERO DE MANIFIESTO</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>CODIGO DE PUERTO</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>PUERTO</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>FECHA Y HORA DE  TRANSMISION AGTE. DE CARGA</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>FECHA Y HORA DE TERMINO DE EMBARQUE</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>ESTADO (MULTA)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -642,40 +708,1392 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB726D33-E6FC-42A3-B62A-EDE71ADD2F2A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>12</v>
+    <row r="1" ht="32.4" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>N°</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>MASTER</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>NUMERO DE PROCESO</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>NUMERO DE MANIFIESTO</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>CODIGO DE PUERTO</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>PUERTO</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>FECHA Y HORA DE  TRANSMISION AGTE. DE CARGA</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>FECHA Y HORA DE TERMINO DE EMBARQUE</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>ESTADO (MULTA)</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Manifiesto de Carga</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Fecha del Manifiesto de Carga</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Manifiesto Desconsolidado</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Fecha del Manifiesto Desconsolidado</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Agente de Carga RUC</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Número de Ticket</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Fecha de Llegada</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Fecha de Término de la Descarga</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Estado del Manifiesto Desconsolidado</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 1709</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>24/06/2026 11:43:39</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 29875</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>30/06/2026 18:45:31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>20606354704</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-43060190</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>08/07/2026 04:25:00</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>09/07/2026 11:09:00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>NUMERADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 1709</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>24/06/2026 11:43:39</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 29875</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>30/06/2026 18:45:31</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>20606354704</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-42389301</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>08/07/2026 04:25:00</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>09/07/2026 11:09:00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>NUMERADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 1703</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>23/06/2026 16:55:26</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 30860</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>06/07/2026 17:23:41</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>20606354704</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-44419381</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>13/07/2026 17:42:00</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>15/07/2026 05:07:00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>NUMERADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 1703</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>23/06/2026 16:55:26</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 30860</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>06/07/2026 17:23:41</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>20606354704</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-44420278</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>13/07/2026 17:42:00</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>15/07/2026 05:07:00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>NUMERADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 1703</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>23/06/2026 16:55:26</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 30860</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>06/07/2026 17:23:41</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>20606354704</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-43805999</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>13/07/2026 17:42:00</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>15/07/2026 05:07:00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>NUMERADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 1703</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>23/06/2026 16:55:26</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 30860</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>06/07/2026 17:23:41</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>20606354704</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-44032582</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>13/07/2026 17:42:00</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>15/07/2026 05:07:00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>NUMERADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 1702</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>23/06/2026 16:06:48</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 30949</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>06/07/2026 17:38:56</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>20606354704</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-43812693</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>10/07/2026 06:35:00</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>11/07/2026 07:34:00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>NUMERADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 1769</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>30/06/2026 17:28:58</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 31090</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>06/07/2026 16:42:34</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>20606354704</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-44033927</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>11/07/2026 16:30:00</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12/07/2026 10:21:00</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>NUMERADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 1769</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>30/06/2026 17:28:58</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 31090</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>06/07/2026 16:42:34</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>20606354704</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-43784464</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>11/07/2026 16:30:00</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>12/07/2026 10:21:00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>NUMERADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 1641</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>17/06/2026 09:14:36</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 31318</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>03/07/2026 18:44:01</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>20606354704</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-43245530</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>12/07/2026 02:00:00</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>13/07/2026 01:41:00</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>NUMERADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 1605</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>15/06/2026 12:09:52</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 31485</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>07/07/2026 17:15:44</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>20606354704</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-44297397</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>15/07/2026 14:30:00</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>15/07/2026 23:46:00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>NUMERADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 1605</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>15/06/2026 12:09:52</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 31485</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>07/07/2026 17:15:44</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>20606354704</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-44033825</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>15/07/2026 14:30:00</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>15/07/2026 23:46:00</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>NUMERADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 1625</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>15/06/2026 15:34:49</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 31968</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>11/07/2026 23:35:37</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>20606354704</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-45120123</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>15/07/2026 14:36:00</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>16/07/2026 06:46:00</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>NUMERADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 1625</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>15/06/2026 15:34:49</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 31968</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>11/07/2026 23:35:37</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>20606354704</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-45122003</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>15/07/2026 14:36:00</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>16/07/2026 06:46:00</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>NUMERADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 1839</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>08/07/2026 10:06:05</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 32022</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>10/07/2026 18:38:45</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>20606354704</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-44830072</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>17/07/2026 19:36:00</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>18/07/2026 16:31:00</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>NUMERADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 1650</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>17/06/2026 17:10:11</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 32433</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>13/07/2026 17:56:29</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>20606354704</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-45406564</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>19/07/2026 13:06:00</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>20/07/2026 13:54:00</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>NUMERADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 1650</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>17/06/2026 17:10:11</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 32433</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>13/07/2026 17:56:29</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>20606354704</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-45402787</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>19/07/2026 13:06:00</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>20/07/2026 13:54:00</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>NUMERADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 1726</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>25/06/2026 16:48:47</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 32894</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>16/07/2026 15:39:33</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>20606354704</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-46125552</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>21/07/2026 09:00:00</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>23/07/2026 06:25:00</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>NUMERADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 1726</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>25/06/2026 16:48:47</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 32894</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>16/07/2026 15:39:33</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>20606354704</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-46123606</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>21/07/2026 09:00:00</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>23/07/2026 06:25:00</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>NUMERADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 1726</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>25/06/2026 16:48:47</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 32894</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>16/07/2026 15:39:33</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>20606354704</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-46130967</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>21/07/2026 09:00:00</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>23/07/2026 06:25:00</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>NUMERADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 1632</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>15/06/2026 17:48:11</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 33355</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>17/07/2026 11:45:30</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>20606354704</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-46314526</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>23/07/2026 09:40:00</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>24/07/2026 10:39:00</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>NUMERADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 1614</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>15/06/2026 13:05:15</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 33714</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>20/07/2026 23:37:34</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>20606354704</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-47133037</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>25/07/2026 15:18:00</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>26/07/2026 16:48:00</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>NUMERADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 1981</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>21/07/2026 16:42:49</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 35179</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>24/07/2026 17:30:26</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>20606354704</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-48022804</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>03/08/2026 16:30:00</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>05/08/2026 07:29:00</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>NUMERADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 1981</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>21/07/2026 16:42:49</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 35179</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>24/07/2026 17:30:26</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>20606354704</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-49431773</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>03/08/2026 16:30:00</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>05/08/2026 07:29:00</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>NUMERADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 1981</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>21/07/2026 16:42:49</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 35179</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>24/07/2026 17:30:26</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>20606354704</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-48036269</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>03/08/2026 16:30:00</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>05/08/2026 07:29:00</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>NUMERADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 1898</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>14/07/2026 12:25:24</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 35429</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>30/07/2026 19:51:46</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>20606354704</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-49663764</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>02/08/2026 23:36:00</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>03/08/2026 16:57:00</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>NUMERADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 1968</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>21/07/2026 12:51:35</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>01-118-1-2026- 35688</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>30/07/2026 11:05:57</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>20606354704</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-49452161</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>05/08/2026 04:36:00</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>06/08/2026 00:49:00</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>NUMERADO</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>